--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/战斗_技能配置表_Combat_SkillConfig.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE0D37DA-BF8C-47E6-B121-6036CC69B00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="201">
   <si>
     <t>技能ID</t>
   </si>
@@ -614,19 +615,41 @@
   </si>
   <si>
     <t>平行阵</t>
+  </si>
+  <si>
+    <t>Skill_Form_Wedge_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Form_Wedge_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远射平行阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Form_Wedge_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Form_Wedge_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Form_Wedge_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>紧凑平行阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,151 +658,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -794,198 +679,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -993,251 +692,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1256,61 +713,17 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1595,23 +1008,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:M65"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M68"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="14.7545454545455" customWidth="1"/>
-    <col min="5" max="5" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="17.1818181818182" customWidth="1"/>
-    <col min="8" max="8" width="53.3636363636364" customWidth="1"/>
-    <col min="9" max="9" width="19.8727272727273" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" customWidth="1"/>
+    <col min="8" max="8" width="53.36328125" customWidth="1"/>
+    <col min="9" max="9" width="19.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1652,7 +1065,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1693,7 +1106,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:13">
+    <row r="3" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1734,7 +1147,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1772,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1810,7 +1223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1848,7 +1261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1886,7 +1299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1924,7 +1337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1962,7 +1375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -2000,7 +1413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -2038,7 +1451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -2076,7 +1489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -2114,7 +1527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -2149,7 +1562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -2184,7 +1597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -2219,7 +1632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -2254,7 +1667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -2289,7 +1702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -2327,7 +1740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>76</v>
       </c>
@@ -2365,7 +1778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>76</v>
       </c>
@@ -2403,7 +1816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>76</v>
       </c>
@@ -2441,7 +1854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>76</v>
       </c>
@@ -2479,7 +1892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>89</v>
       </c>
@@ -2517,7 +1930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>89</v>
       </c>
@@ -2555,7 +1968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -2593,7 +2006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -2631,7 +2044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>89</v>
       </c>
@@ -2669,7 +2082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>102</v>
       </c>
@@ -2707,7 +2120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>102</v>
       </c>
@@ -2745,7 +2158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -2783,7 +2196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>102</v>
       </c>
@@ -2821,7 +2234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>102</v>
       </c>
@@ -2859,7 +2272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>116</v>
       </c>
@@ -2894,7 +2307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>116</v>
       </c>
@@ -2929,7 +2342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>116</v>
       </c>
@@ -2964,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>116</v>
       </c>
@@ -2999,7 +2412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>116</v>
       </c>
@@ -3034,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>128</v>
       </c>
@@ -3072,7 +2485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>128</v>
       </c>
@@ -3110,7 +2523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>128</v>
       </c>
@@ -3148,7 +2561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>128</v>
       </c>
@@ -3186,7 +2599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>128</v>
       </c>
@@ -3224,7 +2637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>141</v>
       </c>
@@ -3259,7 +2672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>141</v>
       </c>
@@ -3294,7 +2707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>141</v>
       </c>
@@ -3329,7 +2742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>141</v>
       </c>
@@ -3364,7 +2777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -3399,7 +2812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>153</v>
       </c>
@@ -3434,7 +2847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>153</v>
       </c>
@@ -3469,7 +2882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>153</v>
       </c>
@@ -3504,7 +2917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -3539,7 +2952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>153</v>
       </c>
@@ -3574,7 +2987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>165</v>
       </c>
@@ -3609,7 +3022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>165</v>
       </c>
@@ -3644,7 +3057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -3679,7 +3092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -3714,7 +3127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>165</v>
       </c>
@@ -3749,7 +3162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>177</v>
       </c>
@@ -3787,7 +3200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>177</v>
       </c>
@@ -3825,7 +3238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>177</v>
       </c>
@@ -3863,7 +3276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -3901,7 +3314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>177</v>
       </c>
@@ -3939,7 +3352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>186</v>
       </c>
@@ -3974,7 +3387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>190</v>
       </c>
@@ -4015,8 +3428,113 @@
         <v>0</v>
       </c>
     </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>194</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>195</v>
+      </c>
+      <c r="D66" t="s">
+        <v>39</v>
+      </c>
+      <c r="E66" t="s">
+        <v>40</v>
+      </c>
+      <c r="G66" t="s">
+        <v>196</v>
+      </c>
+      <c r="H66" t="s">
+        <v>189</v>
+      </c>
+      <c r="I66" t="s">
+        <v>194</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>197</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67" t="s">
+        <v>40</v>
+      </c>
+      <c r="G67" t="s">
+        <v>188</v>
+      </c>
+      <c r="H67" t="s">
+        <v>189</v>
+      </c>
+      <c r="I67" t="s">
+        <v>197</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>198</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>199</v>
+      </c>
+      <c r="D68" t="s">
+        <v>39</v>
+      </c>
+      <c r="E68" t="s">
+        <v>40</v>
+      </c>
+      <c r="G68" t="s">
+        <v>200</v>
+      </c>
+      <c r="H68" t="s">
+        <v>189</v>
+      </c>
+      <c r="I68" t="s">
+        <v>198</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>